--- a/warehouse/templates/export_file/batch_other_shipment_template.xlsx
+++ b/warehouse/templates/export_file/batch_other_shipment_template.xlsx
@@ -27,14 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>柜号</t>
   </si>
   <si>
-    <t>仓点</t>
-  </si>
-  <si>
     <t>唛头</t>
   </si>
   <si>
@@ -44,40 +41,34 @@
     <t>CBM</t>
   </si>
   <si>
-    <t>预约时间</t>
-  </si>
-  <si>
     <t>pickup time</t>
   </si>
   <si>
-    <t>PickUp number</t>
-  </si>
-  <si>
-    <t>预约账号</t>
+    <t>承运公司</t>
+  </si>
+  <si>
+    <t>供应商</t>
   </si>
   <si>
     <t>预约类型</t>
   </si>
   <si>
-    <t>装车类型</t>
-  </si>
-  <si>
     <t>备注</t>
   </si>
   <si>
     <t>发货仓库</t>
   </si>
   <si>
-    <t>是否自动排车</t>
+    <t>车次成本</t>
   </si>
   <si>
     <t>出库时间</t>
   </si>
   <si>
-    <t>是否有出库单</t>
-  </si>
-  <si>
     <t>送达时间</t>
+  </si>
+  <si>
+    <t>NJ-07001</t>
   </si>
 </sst>
 </file>
@@ -90,10 +81,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -584,139 +583,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1065,27 +1067,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="6" max="6" width="14.9090909090909" customWidth="1"/>
-    <col min="7" max="7" width="16.2727272727273" customWidth="1"/>
-    <col min="8" max="8" width="16.3545454545455" customWidth="1"/>
-    <col min="14" max="14" width="12.5454545454545" customWidth="1"/>
-    <col min="16" max="16" width="14.0909090909091" customWidth="1"/>
+    <col min="5" max="6" width="16.2727272727273" customWidth="1"/>
+    <col min="7" max="7" width="9.92727272727273" customWidth="1"/>
+    <col min="10" max="10" width="11.9545454545455" customWidth="1"/>
+    <col min="11" max="11" width="12.8636363636364" customWidth="1"/>
+    <col min="12" max="12" width="11.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1100,32 +1102,25 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="J2" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/warehouse/templates/export_file/batch_other_shipment_template.xlsx
+++ b/warehouse/templates/export_file/batch_other_shipment_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12280"/>
+    <workbookView windowWidth="21450" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -713,7 +713,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -721,6 +721,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1070,7 +1071,8 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="5" max="6" width="16.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="18.3818181818182" customWidth="1"/>
+    <col min="6" max="6" width="16.2727272727273" customWidth="1"/>
     <col min="7" max="7" width="9.92727272727273" customWidth="1"/>
     <col min="10" max="10" width="11.9545454545455" customWidth="1"/>
     <col min="11" max="11" width="12.8636363636364" customWidth="1"/>
@@ -1119,6 +1121,9 @@
       </c>
     </row>
     <row r="2" spans="1:13">
+      <c r="E2" s="3">
+        <v>46170.7083333333</v>
+      </c>
       <c r="J2" t="s">
         <v>13</v>
       </c>
